--- a/artfynd/A 18152-2022 artfynd.xlsx
+++ b/artfynd/A 18152-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18152-2022 artfynd.xlsx
+++ b/artfynd/A 18152-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2198254</v>
+        <v>219263</v>
       </c>
       <c r="B2" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>643</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogssvingel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Drymochloa sylvatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pollich) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335639.9586435558</v>
+        <v>335640</v>
       </c>
       <c r="R2" t="n">
-        <v>6497014.258360717</v>
+        <v>6497014</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1976-04-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1976-04-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>219263</v>
+        <v>2198254</v>
       </c>
       <c r="B3" t="n">
-        <v>97654</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>643</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogssvingel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Drymochloa sylvatica</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pollich) Holub</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335639.9586435558</v>
+        <v>335640</v>
       </c>
       <c r="R3" t="n">
-        <v>6497014.258360717</v>
+        <v>6497014</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>1976-04-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1976-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>2663946</v>
       </c>
       <c r="B4" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335639.9586435558</v>
+        <v>335640</v>
       </c>
       <c r="R4" t="n">
-        <v>6497014.258360717</v>
+        <v>6497014</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>1987-07-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-07-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
